--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827003</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135832019</v>
       </c>
       <c r="B4" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135832015</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135827008</v>
       </c>
       <c r="B6" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135832016</v>
       </c>
       <c r="B7" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135832021</v>
       </c>
       <c r="B8" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135832014</v>
       </c>
       <c r="B9" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135832022</v>
       </c>
       <c r="B10" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135832020</v>
       </c>
       <c r="B11" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135827004</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135827009</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135827012</v>
       </c>
       <c r="B14" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135827007</v>
       </c>
       <c r="B15" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135832012</v>
       </c>
       <c r="B16" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135832017</v>
       </c>
       <c r="B17" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827003</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135832019</v>
       </c>
       <c r="B4" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135832015</v>
       </c>
       <c r="B5" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135827008</v>
       </c>
       <c r="B6" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135832016</v>
       </c>
       <c r="B7" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135832021</v>
       </c>
       <c r="B8" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135832014</v>
       </c>
       <c r="B9" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135832022</v>
       </c>
       <c r="B10" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135827009</v>
       </c>
       <c r="B13" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135827012</v>
       </c>
       <c r="B14" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135827007</v>
       </c>
       <c r="B15" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135832012</v>
       </c>
       <c r="B16" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135832017</v>
       </c>
       <c r="B17" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827003</v>
       </c>
       <c r="B3" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135832019</v>
       </c>
       <c r="B4" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135832015</v>
       </c>
       <c r="B5" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135827008</v>
       </c>
       <c r="B6" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135832016</v>
       </c>
       <c r="B7" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135832021</v>
       </c>
       <c r="B8" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135832014</v>
       </c>
       <c r="B9" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135832022</v>
       </c>
       <c r="B10" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135832020</v>
       </c>
       <c r="B11" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135827004</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135827009</v>
       </c>
       <c r="B13" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135827012</v>
       </c>
       <c r="B14" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135827007</v>
       </c>
       <c r="B15" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135832012</v>
       </c>
       <c r="B16" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135832017</v>
       </c>
       <c r="B17" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827003</v>
       </c>
       <c r="B3" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135832019</v>
       </c>
       <c r="B4" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135832015</v>
       </c>
       <c r="B5" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135827008</v>
       </c>
       <c r="B6" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135832016</v>
       </c>
       <c r="B7" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135832021</v>
       </c>
       <c r="B8" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135832014</v>
       </c>
       <c r="B9" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135832022</v>
       </c>
       <c r="B10" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135832020</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135827004</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135827009</v>
       </c>
       <c r="B13" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135827012</v>
       </c>
       <c r="B14" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135827007</v>
       </c>
       <c r="B15" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135832012</v>
       </c>
       <c r="B16" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135832017</v>
       </c>
       <c r="B17" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827003</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135832019</v>
       </c>
       <c r="B4" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135832015</v>
       </c>
       <c r="B5" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135827008</v>
       </c>
       <c r="B6" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135832016</v>
       </c>
       <c r="B7" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135832021</v>
       </c>
       <c r="B8" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135832014</v>
       </c>
       <c r="B9" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135832022</v>
       </c>
       <c r="B10" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135832020</v>
       </c>
       <c r="B11" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135827004</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135827009</v>
       </c>
       <c r="B13" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135827012</v>
       </c>
       <c r="B14" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135827007</v>
       </c>
       <c r="B15" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135832012</v>
       </c>
       <c r="B16" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135832017</v>
       </c>
       <c r="B17" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827003</v>
       </c>
       <c r="B3" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135832019</v>
       </c>
       <c r="B4" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135832015</v>
       </c>
       <c r="B5" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135827008</v>
       </c>
       <c r="B6" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135832016</v>
       </c>
       <c r="B7" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135832021</v>
       </c>
       <c r="B8" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135832014</v>
       </c>
       <c r="B9" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135832022</v>
       </c>
       <c r="B10" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135827009</v>
       </c>
       <c r="B13" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135827012</v>
       </c>
       <c r="B14" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135827007</v>
       </c>
       <c r="B15" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135832012</v>
       </c>
       <c r="B16" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135832017</v>
       </c>
       <c r="B17" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827003</v>
       </c>
       <c r="B3" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135832019</v>
       </c>
       <c r="B4" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135832015</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135827008</v>
       </c>
       <c r="B6" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135832016</v>
       </c>
       <c r="B7" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135832021</v>
       </c>
       <c r="B8" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135832014</v>
       </c>
       <c r="B9" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135832022</v>
       </c>
       <c r="B10" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135832020</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135827004</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135827009</v>
       </c>
       <c r="B13" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135827012</v>
       </c>
       <c r="B14" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135827007</v>
       </c>
       <c r="B15" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135832012</v>
       </c>
       <c r="B16" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135832017</v>
       </c>
       <c r="B17" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61762-2024 artfynd.xlsx
+++ b/artfynd/A 61762-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135832024</v>
       </c>
       <c r="B2" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135827003</v>
       </c>
       <c r="B3" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135832019</v>
       </c>
       <c r="B4" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135832015</v>
       </c>
       <c r="B5" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135827008</v>
       </c>
       <c r="B6" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135832016</v>
       </c>
       <c r="B7" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135832021</v>
       </c>
       <c r="B8" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135832014</v>
       </c>
       <c r="B9" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135832022</v>
       </c>
       <c r="B10" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135832020</v>
       </c>
       <c r="B11" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135827004</v>
       </c>
       <c r="B12" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135827009</v>
       </c>
       <c r="B13" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135827012</v>
       </c>
       <c r="B14" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135827007</v>
       </c>
       <c r="B15" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135832012</v>
       </c>
       <c r="B16" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135832017</v>
       </c>
       <c r="B17" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
